--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>465</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.365349</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.586386</v>
-      </c>
-      <c r="I2" t="n">
-        <v>283</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.365349</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.586386</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>64069</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.387461</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.60331600000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1046</v>
-      </c>
-      <c r="J3" t="n">
-        <v>43</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.387461</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.603316</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>64698 SGTO.2DO.FAP LAZARO ORREGO MORALES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.358791</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.586764</v>
-      </c>
-      <c r="I4" t="n">
-        <v>852</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.358791</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.586764</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>427</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.35913</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.58384</v>
-      </c>
-      <c r="I5" t="n">
-        <v>207</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.35913</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.58384</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>64661</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.378558999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.61904199999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>238</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.378559</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.619042</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>64668 / LA PERLA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.363754999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.58461</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1429</v>
-      </c>
-      <c r="J7" t="n">
-        <v>58</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.363755</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.58461</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>64789 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.383369999999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.59605000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1258</v>
-      </c>
-      <c r="J8" t="n">
-        <v>50</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.38337</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.59605</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>ELMER JAVIER URRELO CORREA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.384188</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.589123</v>
-      </c>
-      <c r="I9" t="n">
-        <v>567</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.384188</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.589123</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>64865 ALFREDO VARGAS GUERRA / ALFREDO VARGAS GUERRA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.388546</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.568043</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2387</v>
-      </c>
-      <c r="J10" t="n">
-        <v>97</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.388546</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.568043</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>64975 / 64975 - HUSARES DEL PERU / HUSARES DEL PERU</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.378584</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.570443</v>
-      </c>
-      <c r="I11" t="n">
-        <v>798</v>
-      </c>
-      <c r="J11" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.378584</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.570443</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>64353</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.411695</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.660304</v>
-      </c>
-      <c r="I12" t="n">
-        <v>432</v>
-      </c>
-      <c r="J12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.411695</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.660304</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>HIPOLITO UNANUE</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.412265</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.66053599999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>442</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.412265</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.660536</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>234 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.355373</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-74.57428899999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>286</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.355373</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-74.574289</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>301</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.365728000000002</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-74.573352</v>
-      </c>
-      <c r="I15" t="n">
-        <v>200</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.365728000000002</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-74.573352</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>423</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.384064</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-74.569821</v>
-      </c>
-      <c r="I16" t="n">
-        <v>281</v>
-      </c>
-      <c r="J16" t="n">
-        <v>11</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.384064</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-74.569821</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>438 AMADEUS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.36341</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-74.56116</v>
-      </c>
-      <c r="I17" t="n">
-        <v>230</v>
-      </c>
-      <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.36341</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-74.56116</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>64093 EDITA BRITO MAINAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.356282999999999</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-74.578543</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1096</v>
-      </c>
-      <c r="J18" t="n">
-        <v>48</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.356283</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-74.578543</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>64095 / ELIAS AGUIRRE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.355869</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-74.596824</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1234</v>
-      </c>
-      <c r="J19" t="n">
-        <v>49</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.355869</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-74.596824</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>64096</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.359075000000002</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-74.572829</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1770</v>
-      </c>
-      <c r="J20" t="n">
-        <v>57</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.359075000000002</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-74.572829</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>64097 VICTOR PINEDO BARDALES</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.338055000000002</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-74.599537</v>
-      </c>
-      <c r="I21" t="n">
-        <v>668</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.338055000000002</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-74.599537</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>64098-B</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.273539</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-74.639438</v>
-      </c>
-      <c r="I22" t="n">
-        <v>235</v>
-      </c>
-      <c r="J22" t="n">
-        <v>16</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.273539</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-74.639438</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>64103 TENIENTE DIEGO FERRE</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.362019999999999</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-74.57771</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1857</v>
-      </c>
-      <c r="J23" t="n">
-        <v>75</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.36202</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-74.57771</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>64567 MIRAFLORES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.372069</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-74.560321</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1628</v>
-      </c>
-      <c r="J24" t="n">
-        <v>66</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.372069</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-74.560321</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>64673 CORONEL JUAN SILVA BOCANEGRA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.368501999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-74.601607</v>
-      </c>
-      <c r="I25" t="n">
-        <v>765</v>
-      </c>
-      <c r="J25" t="n">
-        <v>36</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.368502</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-74.601607</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>64722</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.384399</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-74.58466900000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>203</v>
-      </c>
-      <c r="J26" t="n">
-        <v>13</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.384399</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-74.584669</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>64896 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.367137</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-74.581457</v>
-      </c>
-      <c r="I27" t="n">
-        <v>443</v>
-      </c>
-      <c r="J27" t="n">
-        <v>17</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.367137</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-74.581457</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>64999</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.3627</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-74.562029</v>
-      </c>
-      <c r="I28" t="n">
-        <v>751</v>
-      </c>
-      <c r="J28" t="n">
-        <v>32</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.3627</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-74.562029</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>APLICACION BILINGUE INTERCULTURAL</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.348941999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-74.586465</v>
-      </c>
-      <c r="I29" t="n">
-        <v>209</v>
-      </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.348942</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-74.586465</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>65005 ECO TURISTICO JUAN LIZARDO DEL AGUILA RENGIFO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.38607</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-74.57989999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>232</v>
-      </c>
-      <c r="J30" t="n">
-        <v>12</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.38607</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-74.5799</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>392</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.371995999999999</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-74.56587500000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>204</v>
-      </c>
-      <c r="J31" t="n">
-        <v>12</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.371996</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-74.565875</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>HOSPITAL AMAZONICO</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.35478</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-74.57375999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>293</v>
-      </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.35478</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-74.57376</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>65092</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.3774</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-74.58903599999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>906</v>
-      </c>
-      <c r="J33" t="n">
-        <v>50</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.3774</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-74.589036</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>65099</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-8.363346999999999</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-74.557481</v>
-      </c>
-      <c r="I34" t="n">
-        <v>254</v>
-      </c>
-      <c r="J34" t="n">
-        <v>15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-8.363347</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-74.557481</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>CRISTIANO PERUANO AMERICANO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-8.381752000000002</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-74.562314</v>
-      </c>
-      <c r="I35" t="n">
-        <v>553</v>
-      </c>
-      <c r="J35" t="n">
-        <v>36</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-8.381752000000002</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-74.562314</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>64094</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-8.3232</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-74.6048</v>
-      </c>
-      <c r="I36" t="n">
-        <v>294</v>
-      </c>
-      <c r="J36" t="n">
-        <v>15</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-8.3232</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-74.6048</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>65166 JUAN PEDRO FLORES DAVILA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-8.363427</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-74.59062400000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>256</v>
-      </c>
-      <c r="J37" t="n">
-        <v>10</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.363427</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-74.590624</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>65325 VICTORIA GRACIA - B</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-8.363083</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-74.612914</v>
-      </c>
-      <c r="I38" t="n">
-        <v>528</v>
-      </c>
-      <c r="J38" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-8.363083</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-74.612914</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>INNOVA SCHOOLS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-8.385512</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-74.55916999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1071</v>
-      </c>
-      <c r="J39" t="n">
-        <v>63</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-8.385512</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-74.55917</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-8.386017000000002</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-74.563294</v>
-      </c>
-      <c r="I40" t="n">
-        <v>463</v>
-      </c>
-      <c r="J40" t="n">
-        <v>27</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-8.386017000000002</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-74.563294</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-8.38598</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-74.5686</v>
-      </c>
-      <c r="I41" t="n">
-        <v>892</v>
-      </c>
-      <c r="J41" t="n">
-        <v>38</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-8.38598</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-74.5686</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>INGENIEROS UNI</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-8.379846000000002</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-74.565229</v>
-      </c>
-      <c r="I42" t="n">
-        <v>557</v>
-      </c>
-      <c r="J42" t="n">
-        <v>31</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-8.379846000000002</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-74.565229</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>813428</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>65166 JUAN PEDRO FLORES DAVILA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.365349</t>
+          <t>-8.363427</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.586386</t>
+          <t>-74.590624</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>494676</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64069</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.387461</t>
+          <t>-8.378559</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.603316</t>
+          <t>-74.619042</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79319</t>
+          <t>499202</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64698 SGTO.2DO.FAP LAZARO ORREGO MORALES</t>
+          <t>423</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.358791</t>
+          <t>-8.384064</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.586764</t>
+          <t>-74.569821</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>493733</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>465</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.35913</t>
+          <t>-8.365349</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.58384</t>
+          <t>-74.586386</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>494676</t>
+          <t>499749</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>65005 ECO TURISTICO JUAN LIZARDO DEL AGUILA RENGIFO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.378559</t>
+          <t>-8.38607</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.619042</t>
+          <t>-74.5799</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>494681</t>
+          <t>499773</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>64668 / LA PERLA</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.363755</t>
+          <t>-8.371996</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.58461</t>
+          <t>-74.565875</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>494921</t>
+          <t>499023</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>64789 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>234 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.38337</t>
+          <t>-8.355373</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.59605</t>
+          <t>-74.574289</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>495044</t>
+          <t>499551</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ELMER JAVIER URRELO CORREA</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.384188</t>
+          <t>-8.384399</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.589123</t>
+          <t>-74.584669</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>495063</t>
+          <t>499730</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>64865 ALFREDO VARGAS GUERRA / ALFREDO VARGAS GUERRA</t>
+          <t>APLICACION BILINGUE INTERCULTURAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.388546</t>
+          <t>-8.348942</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.568043</t>
+          <t>-74.586465</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>495223</t>
+          <t>499805</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64975 / 64975 - HUSARES DEL PERU / HUSARES DEL PERU</t>
+          <t>HOSPITAL AMAZONICO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.378584</t>
+          <t>-8.35478</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.570443</t>
+          <t>-74.57376</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>496454</t>
+          <t>499848</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.411695</t>
+          <t>-8.363347</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.660304</t>
+          <t>-74.557481</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>496878</t>
+          <t>611487</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HIPOLITO UNANUE</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.412265</t>
+          <t>-8.3232</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.660536</t>
+          <t>-74.6048</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>499023</t>
+          <t>499339</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>234 NUESTRA SEÑORA DE LOURDES</t>
+          <t>64098-B</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.355373</t>
+          <t>-8.273539</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.574289</t>
+          <t>-74.639438</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>499061</t>
+          <t>496454</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.365728000000002</t>
+          <t>-8.411695</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.573352</t>
+          <t>-74.660304</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>499202</t>
+          <t>499612</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>64896 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.384064</t>
+          <t>-8.367137</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.569821</t>
+          <t>-74.581457</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>499259</t>
+          <t>830300</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>438 AMADEUS</t>
+          <t>65325 VICTORIA GRACIA - B</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.36341</t>
+          <t>-8.363083</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.56116</t>
+          <t>-74.612914</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>528</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>499283</t>
+          <t>495044</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>64093 EDITA BRITO MAINAS</t>
+          <t>ELMER JAVIER URRELO CORREA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.356283</t>
+          <t>-8.384188</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.578543</t>
+          <t>-74.589123</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>567</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>499301</t>
+          <t>496878</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64095 / ELIAS AGUIRRE</t>
+          <t>HIPOLITO UNANUE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.355869</t>
+          <t>-8.412265</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.596824</t>
+          <t>-74.660536</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>499315</t>
+          <t>853235</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64096</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.359075000000002</t>
+          <t>-8.386017000000002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.572829</t>
+          <t>-74.563294</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>499339</t>
+          <t>79319</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64098-B</t>
+          <t>64698 SGTO.2DO.FAP LAZARO ORREGO MORALES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.273539</t>
+          <t>-8.358791</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.639438</t>
+          <t>-74.586764</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>852</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>499377</t>
+          <t>859505</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>64103 TENIENTE DIEGO FERRE</t>
+          <t>INGENIEROS UNI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.36202</t>
+          <t>-8.379846000000002</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.57771</t>
+          <t>-74.565229</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>499443</t>
+          <t>499631</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>64567 MIRAFLORES</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.372069</t>
+          <t>-8.3627</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.560321</t>
+          <t>-74.562029</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>751</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>499551</t>
+          <t>520326</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>64722</t>
+          <t>CRISTIANO PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.384399</t>
+          <t>-8.381752000000002</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.584669</t>
+          <t>-74.562314</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>553</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>499612</t>
+          <t>857969</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>64896 JOSE ABELARDO QUIÑONES</t>
+          <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.367137</t>
+          <t>-8.38598</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.581457</t>
+          <t>-74.5686</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>892</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>499631</t>
+          <t>495223</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>64999</t>
+          <t>64975 / 64975 - HUSARES DEL PERU / HUSARES DEL PERU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.3627</t>
+          <t>-8.378584</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.562029</t>
+          <t>-74.570443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>798</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>499730</t>
+          <t>75203</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>APLICACION BILINGUE INTERCULTURAL</t>
+          <t>64069</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.348942</t>
+          <t>-8.387461</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.586465</t>
+          <t>-74.603316</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>499749</t>
+          <t>499283</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65005 ECO TURISTICO JUAN LIZARDO DEL AGUILA RENGIFO</t>
+          <t>64093 EDITA BRITO MAINAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.38607</t>
+          <t>-8.356283</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.5799</t>
+          <t>-74.578543</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>499773</t>
+          <t>499301</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>64095 / ELIAS AGUIRRE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.371996</t>
+          <t>-8.355869</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.565875</t>
+          <t>-74.596824</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>499805</t>
+          <t>494921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HOSPITAL AMAZONICO</t>
+          <t>64789 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.35478</t>
+          <t>-8.38337</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.57376</t>
+          <t>-74.59605</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>499848</t>
+          <t>499315</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65099</t>
+          <t>64096</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.363347</t>
+          <t>-8.359075000000002</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.557481</t>
+          <t>-74.572829</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>520326</t>
+          <t>494681</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CRISTIANO PERUANO AMERICANO</t>
+          <t>64668 / LA PERLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.381752000000002</t>
+          <t>-8.363755</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.562314</t>
+          <t>-74.58461</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>611487</t>
+          <t>843492</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.3232</t>
+          <t>-8.385512</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.6048</t>
+          <t>-74.55917</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>813428</t>
+          <t>499443</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65166 JUAN PEDRO FLORES DAVILA</t>
+          <t>64567 MIRAFLORES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.363427</t>
+          <t>-8.372069</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.590624</t>
+          <t>-74.560321</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>830300</t>
+          <t>499377</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65325 VICTORIA GRACIA - B</t>
+          <t>64103 TENIENTE DIEGO FERRE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.363083</t>
+          <t>-8.36202</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.612914</t>
+          <t>-74.57771</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>843492</t>
+          <t>493733</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>427</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.385512</t>
+          <t>-8.35913</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-74.55917</t>
+          <t>-74.58384</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>853235</t>
+          <t>499061</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.386017000000002</t>
+          <t>-8.365728000000002</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.563294</t>
+          <t>-74.573352</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>857969</t>
+          <t>499259</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HORACIO ZEBALLOS GAMEZ</t>
+          <t>438 AMADEUS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.38598</t>
+          <t>-8.36341</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.5686</t>
+          <t>-74.56116</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>859505</t>
+          <t>495063</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INGENIEROS UNI</t>
+          <t>64865 ALFREDO VARGAS GUERRA / ALFREDO VARGAS GUERRA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.379846000000002</t>
+          <t>-8.388546</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-74.565229</t>
+          <t>-74.568043</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.386017000000002</t>
+          <t>-8.386017</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.338055000000002</t>
+          <t>-8.338055</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.379846000000002</t>
+          <t>-8.379846</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.381752000000002</t>
+          <t>-8.381752</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.359075000000002</t>
+          <t>-8.359075</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.365728000000002</t>
+          <t>-8.365728</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>813428</t>
+          <t>859505</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65166 JUAN PEDRO FLORES DAVILA</t>
+          <t>INGENIEROS UNI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.363427</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.590624</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-8.379846000000002</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-74.565229</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>494676</t>
+          <t>857969</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>HORACIO ZEBALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.378559</t>
+          <t>892</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.619042</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-8.38598</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-74.5686</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>499202</t>
+          <t>853235</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>PASCUAL SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.384064</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.569821</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-8.386017000000002</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-74.563294</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>843492</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.365349</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.586386</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-8.385512</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.55917</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>499749</t>
+          <t>830300</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65005 ECO TURISTICO JUAN LIZARDO DEL AGUILA RENGIFO</t>
+          <t>65325 VICTORIA GRACIA - B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.38607</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.5799</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-8.363083</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.612914</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>499773</t>
+          <t>813428</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>65166 JUAN PEDRO FLORES DAVILA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.371996</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.565875</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.363427</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.590624</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>499023</t>
+          <t>611487</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>234 NUESTRA SEÑORA DE LOURDES</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.355373</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.574289</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-8.3232</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.6048</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>499551</t>
+          <t>520326</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>64722</t>
+          <t>CRISTIANO PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.384399</t>
+          <t>553</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.584669</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-8.381752000000002</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.562314</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>499730</t>
+          <t>499848</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>APLICACION BILINGUE INTERCULTURAL</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.348942</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.586465</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-8.363347</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.557481</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>499805</t>
+          <t>499829</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HOSPITAL AMAZONICO</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.35478</t>
+          <t>906</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.57376</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-8.3774</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.589036</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>499848</t>
+          <t>499805</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65099</t>
+          <t>HOSPITAL AMAZONICO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.363347</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.557481</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-8.35478</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.57376</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>611487</t>
+          <t>499773</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.3232</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.6048</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-8.371996</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.565875</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>499339</t>
+          <t>499749</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>64098-B</t>
+          <t>65005 ECO TURISTICO JUAN LIZARDO DEL AGUILA RENGIFO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.273539</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.639438</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-8.38607</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.5799</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>496454</t>
+          <t>499730</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>APLICACION BILINGUE INTERCULTURAL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.411695</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.660304</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-8.348942</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.586465</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>499612</t>
+          <t>499631</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>64896 JOSE ABELARDO QUIÑONES</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.367137</t>
+          <t>751</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.581457</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-8.3627</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.562029</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>830300</t>
+          <t>499612</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65325 VICTORIA GRACIA - B</t>
+          <t>64896 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.363083</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.612914</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>-8.367137</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-74.581457</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>495044</t>
+          <t>499551</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ELMER JAVIER URRELO CORREA</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.384188</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.589123</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>-8.384399</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-74.584669</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>496878</t>
+          <t>499532</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HIPOLITO UNANUE</t>
+          <t>64673 CORONEL JUAN SILVA BOCANEGRA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.412265</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.660536</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-8.368502</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-74.601607</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>853235</t>
+          <t>499443</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS</t>
+          <t>64567 MIRAFLORES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.386017</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.563294</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>-8.372069</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-74.560321</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>499320</t>
+          <t>499377</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>64097 VICTOR PINEDO BARDALES</t>
+          <t>64103 TENIENTE DIEGO FERRE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.338055</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.599537</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>-8.36202</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-74.57771</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79319</t>
+          <t>499339</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64698 SGTO.2DO.FAP LAZARO ORREGO MORALES</t>
+          <t>64098-B</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.358791</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.586764</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>-8.273539</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-74.639438</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>859505</t>
+          <t>499320</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>INGENIEROS UNI</t>
+          <t>64097 VICTOR PINEDO BARDALES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.379846</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.565229</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-8.338055000000002</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-74.599537</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>499631</t>
+          <t>499315</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>64999</t>
+          <t>64096</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.3627</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.562029</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>-8.359075000000002</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-74.572829</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>499532</t>
+          <t>499301</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>64673 CORONEL JUAN SILVA BOCANEGRA</t>
+          <t>64095 / ELIAS AGUIRRE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.368502</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-74.601607</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>-8.355869</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.596824</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>520326</t>
+          <t>499283</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CRISTIANO PERUANO AMERICANO</t>
+          <t>64093 EDITA BRITO MAINAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.381752</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.562314</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>-8.356283</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.578543</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>857969</t>
+          <t>499259</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HORACIO ZEBALLOS GAMEZ</t>
+          <t>438 AMADEUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.38598</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.5686</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>-8.36341</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-74.56116</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>495223</t>
+          <t>499202</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>64975 / 64975 - HUSARES DEL PERU / HUSARES DEL PERU</t>
+          <t>423</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.378584</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.570443</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>-8.384064</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-74.569821</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>499061</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>64069</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.387461</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.603316</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>-8.365728000000002</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-74.573352</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>499283</t>
+          <t>499023</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>64093 EDITA BRITO MAINAS</t>
+          <t>234 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.356283</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.578543</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>-8.355373</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-74.574289</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>499301</t>
+          <t>496878</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>64095 / ELIAS AGUIRRE</t>
+          <t>HIPOLITO UNANUE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.355869</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.596824</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>-8.412265</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-74.660536</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>494921</t>
+          <t>496454</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>64789 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.38337</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.59605</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>-8.411695</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-74.660304</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>499829</t>
+          <t>495223</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>64975 / 64975 - HUSARES DEL PERU / HUSARES DEL PERU</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.3774</t>
+          <t>798</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-74.589036</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>-8.378584</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-74.570443</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>499315</t>
+          <t>495063</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>64096</t>
+          <t>64865 ALFREDO VARGAS GUERRA / ALFREDO VARGAS GUERRA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.359075</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.572829</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>-8.388546</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-74.568043</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>494681</t>
+          <t>495044</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>64668 / LA PERLA</t>
+          <t>ELMER JAVIER URRELO CORREA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.363755</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.58461</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>-8.384188</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-74.589123</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>843492</t>
+          <t>494921</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>64789 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.385512</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.55917</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>-8.38337</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-74.59605</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>499443</t>
+          <t>494681</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>64567 MIRAFLORES</t>
+          <t>64668 / LA PERLA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.372069</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.560321</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>-8.363755</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-74.58461</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>499377</t>
+          <t>494676</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>64103 TENIENTE DIEGO FERRE</t>
+          <t>64661</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.36202</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.57771</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>-8.378559</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-74.619042</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>-8.35913</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-74.58384</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>499061</t>
+          <t>079319</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>64698 SGTO.2DO.FAP LAZARO ORREGO MORALES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.365728</t>
+          <t>852</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.573352</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-8.358791</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-74.586764</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>499259</t>
+          <t>075203</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>438 AMADEUS</t>
+          <t>64069</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.36341</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.56116</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-8.387461</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-74.603316</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>495063</t>
+          <t>075000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>64865 ALFREDO VARGAS GUERRA / ALFREDO VARGAS GUERRA</t>
+          <t>465</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.388546</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-74.568043</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>-8.365349</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-74.586386</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
